--- a/sample/products.xlsx
+++ b/sample/products.xlsx
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>soap, lux, kulikum soap</t>
+          <t>lux, kulikum soap</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>powder, talc</t>
+          <t>talc, talcum</t>
         </is>
       </c>
     </row>
